--- a/TI_Lab2/lfsr35_table_60.xlsx
+++ b/TI_Lab2/lfsr35_table_60.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yaroslavsts/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yaroslavsts/Documents/TI_Labs/TI_Lab2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{D9D81E8E-496C-3749-A9C3-736780970A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CDA618-A4FD-D944-8B51-7AEDF36ACDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="3260" windowWidth="27440" windowHeight="16240"/>
+    <workbookView xWindow="3960" yWindow="660" windowWidth="27440" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lfsr35_table_60" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -922,7 +922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1053,109 +1053,109 @@
         <v>1</v>
       </c>
       <c r="C2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2" s="3">
         <v>1</v>
       </c>
       <c r="AK2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.2">
@@ -1163,112 +1163,112 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" s="4">
         <v>1</v>
       </c>
       <c r="AJ3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.2">
@@ -1276,109 +1276,109 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH4" s="3">
         <v>1</v>
       </c>
       <c r="AI4" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="2">
         <v>1</v>
@@ -1389,106 +1389,106 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" s="3">
         <v>1</v>
       </c>
       <c r="AH5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3">
         <v>1</v>
@@ -1502,103 +1502,103 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" s="3">
         <v>1</v>
       </c>
       <c r="AG6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="4">
         <v>1</v>
@@ -1607,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="AK6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.2">
@@ -1615,100 +1615,100 @@
         <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3">
         <v>1</v>
       </c>
       <c r="AF7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="3">
         <v>1</v>
@@ -1717,10 +1717,10 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.2">
@@ -1728,97 +1728,97 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" s="3">
         <v>1</v>
       </c>
       <c r="AE8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="3">
         <v>1</v>
@@ -1827,10 +1827,10 @@
         <v>1</v>
       </c>
       <c r="AI8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="2">
         <v>1</v>
@@ -1841,94 +1841,94 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" s="3">
         <v>1</v>
       </c>
       <c r="AD9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3">
         <v>1</v>
@@ -1937,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="AH9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3">
         <v>1</v>
@@ -1954,91 +1954,91 @@
         <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="3">
         <v>1</v>
       </c>
       <c r="AC10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3">
         <v>1</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="AG10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="4">
         <v>1</v>
@@ -2059,7 +2059,7 @@
         <v>1</v>
       </c>
       <c r="AK10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.2">
@@ -2067,88 +2067,88 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="3">
         <v>1</v>
       </c>
       <c r="AB11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="3">
         <v>1</v>
@@ -2157,10 +2157,10 @@
         <v>1</v>
       </c>
       <c r="AF11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="3">
         <v>1</v>
@@ -2169,10 +2169,10 @@
         <v>1</v>
       </c>
       <c r="AJ11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.2">
@@ -2180,85 +2180,85 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="3">
         <v>1</v>
       </c>
       <c r="AA12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="3">
         <v>1</v>
@@ -2267,10 +2267,10 @@
         <v>1</v>
       </c>
       <c r="AE12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="3">
         <v>1</v>
@@ -2279,10 +2279,10 @@
         <v>1</v>
       </c>
       <c r="AI12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="2">
         <v>1</v>
@@ -2293,82 +2293,82 @@
         <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="3">
         <v>1</v>
       </c>
       <c r="Z13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="3">
         <v>1</v>
@@ -2377,10 +2377,10 @@
         <v>1</v>
       </c>
       <c r="AD13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF13" s="3">
         <v>1</v>
@@ -2389,10 +2389,10 @@
         <v>1</v>
       </c>
       <c r="AH13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="3">
         <v>1</v>
@@ -2406,79 +2406,79 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="3">
         <v>1</v>
       </c>
       <c r="Y14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>1</v>
@@ -2487,10 +2487,10 @@
         <v>1</v>
       </c>
       <c r="AC14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="3">
         <v>1</v>
@@ -2499,10 +2499,10 @@
         <v>1</v>
       </c>
       <c r="AG14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="4">
         <v>1</v>
@@ -2511,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="AK14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.2">
@@ -2519,76 +2519,76 @@
         <v>14</v>
       </c>
       <c r="B15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="3">
         <v>1</v>
       </c>
       <c r="X15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3">
         <v>1</v>
@@ -2597,10 +2597,10 @@
         <v>1</v>
       </c>
       <c r="AB15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="3">
         <v>1</v>
@@ -2609,10 +2609,10 @@
         <v>1</v>
       </c>
       <c r="AF15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" s="3">
         <v>1</v>
@@ -2621,10 +2621,10 @@
         <v>1</v>
       </c>
       <c r="AJ15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.2">
@@ -2632,73 +2632,73 @@
         <v>15</v>
       </c>
       <c r="B16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="3">
         <v>1</v>
       </c>
       <c r="W16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="3">
         <v>1</v>
@@ -2707,10 +2707,10 @@
         <v>1</v>
       </c>
       <c r="AA16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="3">
         <v>1</v>
@@ -2719,10 +2719,10 @@
         <v>1</v>
       </c>
       <c r="AE16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="3">
         <v>1</v>
@@ -2731,10 +2731,10 @@
         <v>1</v>
       </c>
       <c r="AI16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="2">
         <v>1</v>
@@ -2745,70 +2745,70 @@
         <v>16</v>
       </c>
       <c r="B17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" s="3">
         <v>1</v>
       </c>
       <c r="V17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" s="3">
         <v>1</v>
@@ -2817,10 +2817,10 @@
         <v>1</v>
       </c>
       <c r="Z17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="3">
         <v>1</v>
@@ -2829,10 +2829,10 @@
         <v>1</v>
       </c>
       <c r="AD17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="3">
         <v>1</v>
@@ -2841,10 +2841,10 @@
         <v>1</v>
       </c>
       <c r="AH17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" s="3">
         <v>1</v>
@@ -2858,67 +2858,67 @@
         <v>17</v>
       </c>
       <c r="B18" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" s="3">
         <v>1</v>
@@ -2927,10 +2927,10 @@
         <v>1</v>
       </c>
       <c r="Y18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3">
         <v>1</v>
@@ -2939,10 +2939,10 @@
         <v>1</v>
       </c>
       <c r="AC18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="3">
         <v>1</v>
@@ -2951,10 +2951,10 @@
         <v>1</v>
       </c>
       <c r="AG18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="4">
         <v>1</v>
@@ -2963,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="AK18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.2">
@@ -2971,64 +2971,64 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="3">
         <v>1</v>
       </c>
       <c r="T19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="3">
         <v>1</v>
@@ -3037,10 +3037,10 @@
         <v>1</v>
       </c>
       <c r="X19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="3">
         <v>1</v>
@@ -3049,10 +3049,10 @@
         <v>1</v>
       </c>
       <c r="AB19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" s="3">
         <v>1</v>
@@ -3061,10 +3061,10 @@
         <v>1</v>
       </c>
       <c r="AF19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH19" s="3">
         <v>1</v>
@@ -3073,10 +3073,10 @@
         <v>1</v>
       </c>
       <c r="AJ19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.2">
@@ -3084,61 +3084,61 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="3">
         <v>1</v>
       </c>
       <c r="S20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>1</v>
@@ -3147,10 +3147,10 @@
         <v>1</v>
       </c>
       <c r="W20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>1</v>
@@ -3159,10 +3159,10 @@
         <v>1</v>
       </c>
       <c r="AA20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>1</v>
@@ -3171,10 +3171,10 @@
         <v>1</v>
       </c>
       <c r="AE20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="3">
         <v>1</v>
@@ -3183,10 +3183,10 @@
         <v>1</v>
       </c>
       <c r="AI20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="2">
         <v>1</v>
@@ -3197,58 +3197,58 @@
         <v>20</v>
       </c>
       <c r="B21" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="3">
         <v>1</v>
       </c>
       <c r="R21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" s="3">
         <v>1</v>
@@ -3257,10 +3257,10 @@
         <v>1</v>
       </c>
       <c r="V21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" s="3">
         <v>1</v>
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="Z21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="3">
         <v>1</v>
@@ -3281,10 +3281,10 @@
         <v>1</v>
       </c>
       <c r="AD21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="3">
         <v>1</v>
@@ -3293,10 +3293,10 @@
         <v>1</v>
       </c>
       <c r="AH21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" s="3">
         <v>1</v>
@@ -3310,55 +3310,55 @@
         <v>21</v>
       </c>
       <c r="B22" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="3">
         <v>1</v>
       </c>
       <c r="Q22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>1</v>
@@ -3367,10 +3367,10 @@
         <v>1</v>
       </c>
       <c r="U22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" s="3">
         <v>1</v>
@@ -3379,10 +3379,10 @@
         <v>1</v>
       </c>
       <c r="Y22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="3">
         <v>1</v>
@@ -3391,10 +3391,10 @@
         <v>1</v>
       </c>
       <c r="AC22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="3">
         <v>1</v>
@@ -3403,10 +3403,10 @@
         <v>1</v>
       </c>
       <c r="AG22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="4">
         <v>1</v>
@@ -3415,7 +3415,7 @@
         <v>1</v>
       </c>
       <c r="AK22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.2">
@@ -3423,52 +3423,52 @@
         <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="3">
         <v>1</v>
       </c>
       <c r="P23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3">
         <v>1</v>
@@ -3477,10 +3477,10 @@
         <v>1</v>
       </c>
       <c r="T23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
         <v>1</v>
@@ -3489,10 +3489,10 @@
         <v>1</v>
       </c>
       <c r="X23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3">
         <v>1</v>
@@ -3501,10 +3501,10 @@
         <v>1</v>
       </c>
       <c r="AB23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="3">
         <v>1</v>
@@ -3513,10 +3513,10 @@
         <v>1</v>
       </c>
       <c r="AF23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23" s="3">
         <v>1</v>
@@ -3525,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.2">
@@ -3536,49 +3536,49 @@
         <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="3">
         <v>1</v>
       </c>
       <c r="O24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="3">
         <v>1</v>
@@ -3587,10 +3587,10 @@
         <v>1</v>
       </c>
       <c r="S24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3">
         <v>1</v>
@@ -3599,10 +3599,10 @@
         <v>1</v>
       </c>
       <c r="W24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
         <v>1</v>
@@ -3611,10 +3611,10 @@
         <v>1</v>
       </c>
       <c r="AA24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="3">
         <v>1</v>
@@ -3623,10 +3623,10 @@
         <v>1</v>
       </c>
       <c r="AE24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="3">
         <v>1</v>
@@ -3635,10 +3635,10 @@
         <v>1</v>
       </c>
       <c r="AI24" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="2">
         <v>1</v>
@@ -3649,46 +3649,46 @@
         <v>24</v>
       </c>
       <c r="B25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="3">
         <v>1</v>
       </c>
       <c r="N25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="3">
         <v>1</v>
@@ -3697,10 +3697,10 @@
         <v>1</v>
       </c>
       <c r="R25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
@@ -3709,10 +3709,10 @@
         <v>1</v>
       </c>
       <c r="V25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25" s="3">
         <v>1</v>
@@ -3721,10 +3721,10 @@
         <v>1</v>
       </c>
       <c r="Z25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="3">
         <v>1</v>
@@ -3733,10 +3733,10 @@
         <v>1</v>
       </c>
       <c r="AD25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF25" s="3">
         <v>1</v>
@@ -3745,10 +3745,10 @@
         <v>1</v>
       </c>
       <c r="AH25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" s="3">
         <v>1</v>
@@ -3762,43 +3762,43 @@
         <v>25</v>
       </c>
       <c r="B26" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="3">
         <v>1</v>
       </c>
       <c r="M26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3">
         <v>1</v>
@@ -3807,10 +3807,10 @@
         <v>1</v>
       </c>
       <c r="Q26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
         <v>1</v>
@@ -3819,10 +3819,10 @@
         <v>1</v>
       </c>
       <c r="U26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" s="3">
         <v>1</v>
@@ -3831,10 +3831,10 @@
         <v>1</v>
       </c>
       <c r="Y26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="3">
         <v>1</v>
@@ -3843,10 +3843,10 @@
         <v>1</v>
       </c>
       <c r="AC26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="3">
         <v>1</v>
@@ -3855,10 +3855,10 @@
         <v>1</v>
       </c>
       <c r="AG26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="4">
         <v>1</v>
@@ -3867,7 +3867,7 @@
         <v>1</v>
       </c>
       <c r="AK26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.2">
@@ -3875,40 +3875,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="3">
         <v>1</v>
       </c>
       <c r="L27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="3">
         <v>1</v>
@@ -3917,10 +3917,10 @@
         <v>1</v>
       </c>
       <c r="P27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" s="3">
         <v>1</v>
@@ -3929,10 +3929,10 @@
         <v>1</v>
       </c>
       <c r="T27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
         <v>1</v>
@@ -3941,10 +3941,10 @@
         <v>1</v>
       </c>
       <c r="X27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="3">
         <v>1</v>
@@ -3953,10 +3953,10 @@
         <v>1</v>
       </c>
       <c r="AB27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="3">
         <v>1</v>
@@ -3965,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="AF27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH27" s="3">
         <v>1</v>
@@ -3977,10 +3977,10 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.2">
@@ -3988,37 +3988,37 @@
         <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="3">
         <v>1</v>
       </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="3">
         <v>1</v>
@@ -4027,10 +4027,10 @@
         <v>1</v>
       </c>
       <c r="O28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
@@ -4039,10 +4039,10 @@
         <v>1</v>
       </c>
       <c r="S28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" s="3">
         <v>1</v>
@@ -4051,10 +4051,10 @@
         <v>1</v>
       </c>
       <c r="W28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" s="3">
         <v>1</v>
@@ -4063,10 +4063,10 @@
         <v>1</v>
       </c>
       <c r="AA28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC28" s="3">
         <v>1</v>
@@ -4075,10 +4075,10 @@
         <v>1</v>
       </c>
       <c r="AE28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" s="3">
         <v>1</v>
@@ -4087,10 +4087,10 @@
         <v>1</v>
       </c>
       <c r="AI28" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="2">
         <v>1</v>
@@ -4101,34 +4101,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="3">
         <v>1</v>
       </c>
       <c r="J29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3">
         <v>1</v>
@@ -4137,10 +4137,10 @@
         <v>1</v>
       </c>
       <c r="N29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="3">
         <v>1</v>
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="R29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
@@ -4161,10 +4161,10 @@
         <v>1</v>
       </c>
       <c r="V29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29" s="3">
         <v>1</v>
@@ -4173,10 +4173,10 @@
         <v>1</v>
       </c>
       <c r="Z29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="3">
         <v>1</v>
@@ -4185,10 +4185,10 @@
         <v>1</v>
       </c>
       <c r="AD29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF29" s="3">
         <v>1</v>
@@ -4197,10 +4197,10 @@
         <v>1</v>
       </c>
       <c r="AH29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" s="3">
         <v>1</v>
@@ -4214,31 +4214,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3">
         <v>1</v>
       </c>
       <c r="I30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="3">
         <v>1</v>
@@ -4247,10 +4247,10 @@
         <v>1</v>
       </c>
       <c r="M30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="3">
         <v>1</v>
@@ -4259,10 +4259,10 @@
         <v>1</v>
       </c>
       <c r="Q30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" s="3">
         <v>1</v>
@@ -4271,10 +4271,10 @@
         <v>1</v>
       </c>
       <c r="U30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W30" s="3">
         <v>1</v>
@@ -4283,10 +4283,10 @@
         <v>1</v>
       </c>
       <c r="Y30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="3">
         <v>1</v>
@@ -4295,10 +4295,10 @@
         <v>1</v>
       </c>
       <c r="AC30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="3">
         <v>1</v>
@@ -4307,10 +4307,10 @@
         <v>1</v>
       </c>
       <c r="AG30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="4">
         <v>1</v>
@@ -4319,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="AK30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.2">
@@ -4327,28 +4327,28 @@
         <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
       </c>
       <c r="H31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3">
         <v>1</v>
@@ -4357,10 +4357,10 @@
         <v>1</v>
       </c>
       <c r="L31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="3">
         <v>1</v>
@@ -4369,10 +4369,10 @@
         <v>1</v>
       </c>
       <c r="P31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" s="3">
         <v>1</v>
@@ -4381,10 +4381,10 @@
         <v>1</v>
       </c>
       <c r="T31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="3">
         <v>1</v>
@@ -4393,10 +4393,10 @@
         <v>1</v>
       </c>
       <c r="X31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="3">
         <v>1</v>
@@ -4405,10 +4405,10 @@
         <v>1</v>
       </c>
       <c r="AB31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD31" s="3">
         <v>1</v>
@@ -4417,10 +4417,10 @@
         <v>1</v>
       </c>
       <c r="AF31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH31" s="3">
         <v>1</v>
@@ -4429,10 +4429,10 @@
         <v>1</v>
       </c>
       <c r="AJ31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.2">
@@ -4440,25 +4440,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="G32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>1</v>
@@ -4467,10 +4467,10 @@
         <v>1</v>
       </c>
       <c r="K32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>1</v>
@@ -4479,10 +4479,10 @@
         <v>1</v>
       </c>
       <c r="O32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
@@ -4491,10 +4491,10 @@
         <v>1</v>
       </c>
       <c r="S32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>1</v>
@@ -4503,10 +4503,10 @@
         <v>1</v>
       </c>
       <c r="W32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>1</v>
@@ -4515,10 +4515,10 @@
         <v>1</v>
       </c>
       <c r="AA32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>1</v>
@@ -4527,10 +4527,10 @@
         <v>1</v>
       </c>
       <c r="AE32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="3">
         <v>1</v>
@@ -4539,10 +4539,10 @@
         <v>1</v>
       </c>
       <c r="AI32" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="2">
         <v>1</v>
@@ -4553,22 +4553,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="3">
         <v>1</v>
       </c>
       <c r="F33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
         <v>1</v>
@@ -4577,10 +4577,10 @@
         <v>1</v>
       </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3">
         <v>1</v>
@@ -4589,10 +4589,10 @@
         <v>1</v>
       </c>
       <c r="N33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="3">
         <v>1</v>
@@ -4601,10 +4601,10 @@
         <v>1</v>
       </c>
       <c r="R33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
@@ -4613,10 +4613,10 @@
         <v>1</v>
       </c>
       <c r="V33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" s="3">
         <v>1</v>
@@ -4625,10 +4625,10 @@
         <v>1</v>
       </c>
       <c r="Z33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="3">
         <v>1</v>
@@ -4637,10 +4637,10 @@
         <v>1</v>
       </c>
       <c r="AD33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF33" s="3">
         <v>1</v>
@@ -4649,10 +4649,10 @@
         <v>1</v>
       </c>
       <c r="AH33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="3">
         <v>1</v>
@@ -4666,19 +4666,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
       </c>
       <c r="E34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -4687,10 +4687,10 @@
         <v>1</v>
       </c>
       <c r="I34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="3">
         <v>1</v>
@@ -4699,10 +4699,10 @@
         <v>1</v>
       </c>
       <c r="M34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3">
         <v>1</v>
@@ -4711,10 +4711,10 @@
         <v>1</v>
       </c>
       <c r="Q34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" s="3">
         <v>1</v>
@@ -4723,10 +4723,10 @@
         <v>1</v>
       </c>
       <c r="U34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" s="3">
         <v>1</v>
@@ -4735,10 +4735,10 @@
         <v>1</v>
       </c>
       <c r="Y34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="3">
         <v>1</v>
@@ -4747,10 +4747,10 @@
         <v>1</v>
       </c>
       <c r="AC34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE34" s="3">
         <v>1</v>
@@ -4759,10 +4759,10 @@
         <v>1</v>
       </c>
       <c r="AG34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="4">
         <v>1</v>
@@ -4771,7 +4771,7 @@
         <v>1</v>
       </c>
       <c r="AK34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.2">
@@ -4779,16 +4779,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="3">
         <v>1</v>
       </c>
       <c r="D35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
@@ -4797,10 +4797,10 @@
         <v>1</v>
       </c>
       <c r="H35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
         <v>1</v>
@@ -4809,10 +4809,10 @@
         <v>1</v>
       </c>
       <c r="L35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3">
         <v>1</v>
@@ -4821,10 +4821,10 @@
         <v>1</v>
       </c>
       <c r="P35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3">
         <v>1</v>
@@ -4833,10 +4833,10 @@
         <v>1</v>
       </c>
       <c r="T35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
         <v>1</v>
@@ -4845,10 +4845,10 @@
         <v>1</v>
       </c>
       <c r="X35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3">
         <v>1</v>
@@ -4857,10 +4857,10 @@
         <v>1</v>
       </c>
       <c r="AB35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" s="3">
         <v>1</v>
@@ -4869,10 +4869,10 @@
         <v>1</v>
       </c>
       <c r="AF35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH35" s="3">
         <v>1</v>
@@ -4881,10 +4881,10 @@
         <v>1</v>
       </c>
       <c r="AJ35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.2">
@@ -4895,10 +4895,10 @@
         <v>1</v>
       </c>
       <c r="C36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3">
         <v>1</v>
@@ -4907,10 +4907,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3">
         <v>1</v>
@@ -4919,10 +4919,10 @@
         <v>1</v>
       </c>
       <c r="K36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="3">
         <v>1</v>
@@ -4931,10 +4931,10 @@
         <v>1</v>
       </c>
       <c r="O36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
@@ -4943,10 +4943,10 @@
         <v>1</v>
       </c>
       <c r="S36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" s="3">
         <v>1</v>
@@ -4955,10 +4955,10 @@
         <v>1</v>
       </c>
       <c r="W36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="3">
         <v>1</v>
@@ -4967,10 +4967,10 @@
         <v>1</v>
       </c>
       <c r="AA36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" s="3">
         <v>1</v>
@@ -4979,10 +4979,10 @@
         <v>1</v>
       </c>
       <c r="AE36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" s="3">
         <v>1</v>
@@ -4991,13 +4991,13 @@
         <v>1</v>
       </c>
       <c r="AI36" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.2">
@@ -5005,10 +5005,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -5017,10 +5017,10 @@
         <v>1</v>
       </c>
       <c r="F37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="3">
         <v>1</v>
@@ -5029,10 +5029,10 @@
         <v>1</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="3">
         <v>1</v>
@@ -5041,10 +5041,10 @@
         <v>1</v>
       </c>
       <c r="N37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" s="3">
         <v>1</v>
@@ -5053,10 +5053,10 @@
         <v>1</v>
       </c>
       <c r="R37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
@@ -5065,10 +5065,10 @@
         <v>1</v>
       </c>
       <c r="V37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" s="3">
         <v>1</v>
@@ -5077,10 +5077,10 @@
         <v>1</v>
       </c>
       <c r="Z37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="3">
         <v>1</v>
@@ -5089,10 +5089,10 @@
         <v>1</v>
       </c>
       <c r="AD37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF37" s="3">
         <v>1</v>
@@ -5101,13 +5101,13 @@
         <v>1</v>
       </c>
       <c r="AH37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" s="2">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -5127,10 +5127,10 @@
         <v>1</v>
       </c>
       <c r="E38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -5139,10 +5139,10 @@
         <v>1</v>
       </c>
       <c r="I38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="3">
         <v>1</v>
@@ -5151,10 +5151,10 @@
         <v>1</v>
       </c>
       <c r="M38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3">
         <v>1</v>
@@ -5163,10 +5163,10 @@
         <v>1</v>
       </c>
       <c r="Q38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="3">
         <v>1</v>
@@ -5175,10 +5175,10 @@
         <v>1</v>
       </c>
       <c r="U38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W38" s="3">
         <v>1</v>
@@ -5187,10 +5187,10 @@
         <v>1</v>
       </c>
       <c r="Y38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="3">
         <v>1</v>
@@ -5199,10 +5199,10 @@
         <v>1</v>
       </c>
       <c r="AC38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE38" s="3">
         <v>1</v>
@@ -5211,13 +5211,13 @@
         <v>1</v>
       </c>
       <c r="AG38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ38" s="3">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
@@ -5249,10 +5249,10 @@
         <v>1</v>
       </c>
       <c r="H39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="3">
         <v>1</v>
@@ -5261,10 +5261,10 @@
         <v>1</v>
       </c>
       <c r="L39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" s="3">
         <v>1</v>
@@ -5273,10 +5273,10 @@
         <v>1</v>
       </c>
       <c r="P39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" s="3">
         <v>1</v>
@@ -5285,10 +5285,10 @@
         <v>1</v>
       </c>
       <c r="T39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="3">
         <v>1</v>
@@ -5297,10 +5297,10 @@
         <v>1</v>
       </c>
       <c r="X39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="3">
         <v>1</v>
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="AB39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD39" s="3">
         <v>1</v>
@@ -5321,13 +5321,13 @@
         <v>1</v>
       </c>
       <c r="AF39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" s="4">
         <v>0</v>
@@ -5347,10 +5347,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="3">
         <v>1</v>
@@ -5359,10 +5359,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3">
         <v>1</v>
@@ -5371,10 +5371,10 @@
         <v>1</v>
       </c>
       <c r="K40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="3">
         <v>1</v>
@@ -5383,10 +5383,10 @@
         <v>1</v>
       </c>
       <c r="O40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
@@ -5395,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="S40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U40" s="3">
         <v>1</v>
@@ -5407,10 +5407,10 @@
         <v>1</v>
       </c>
       <c r="W40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="3">
         <v>1</v>
@@ -5419,10 +5419,10 @@
         <v>1</v>
       </c>
       <c r="AA40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC40" s="3">
         <v>1</v>
@@ -5431,13 +5431,13 @@
         <v>1</v>
       </c>
       <c r="AE40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH40" s="3">
         <v>0</v>
@@ -5457,10 +5457,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="3">
         <v>1</v>
@@ -5469,10 +5469,10 @@
         <v>1</v>
       </c>
       <c r="F41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
@@ -5481,10 +5481,10 @@
         <v>1</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
         <v>1</v>
@@ -5493,10 +5493,10 @@
         <v>1</v>
       </c>
       <c r="N41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P41" s="3">
         <v>1</v>
@@ -5505,10 +5505,10 @@
         <v>1</v>
       </c>
       <c r="R41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
@@ -5517,10 +5517,10 @@
         <v>1</v>
       </c>
       <c r="V41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X41" s="3">
         <v>1</v>
@@ -5529,10 +5529,10 @@
         <v>1</v>
       </c>
       <c r="Z41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="3">
         <v>1</v>
@@ -5541,13 +5541,13 @@
         <v>1</v>
       </c>
       <c r="AD41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" s="3">
         <v>0</v>
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.2">
@@ -5570,7 +5570,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -5579,10 +5579,10 @@
         <v>1</v>
       </c>
       <c r="E42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -5591,10 +5591,10 @@
         <v>1</v>
       </c>
       <c r="I42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>1</v>
@@ -5603,10 +5603,10 @@
         <v>1</v>
       </c>
       <c r="M42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="3">
         <v>1</v>
@@ -5615,10 +5615,10 @@
         <v>1</v>
       </c>
       <c r="Q42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" s="3">
         <v>1</v>
@@ -5627,10 +5627,10 @@
         <v>1</v>
       </c>
       <c r="U42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W42" s="3">
         <v>1</v>
@@ -5639,10 +5639,10 @@
         <v>1</v>
       </c>
       <c r="Y42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="3">
         <v>1</v>
@@ -5651,13 +5651,13 @@
         <v>1</v>
       </c>
       <c r="AC42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -5672,10 +5672,10 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.2">
@@ -5689,10 +5689,10 @@
         <v>1</v>
       </c>
       <c r="D43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3">
         <v>1</v>
@@ -5701,10 +5701,10 @@
         <v>1</v>
       </c>
       <c r="H43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3">
         <v>1</v>
@@ -5713,10 +5713,10 @@
         <v>1</v>
       </c>
       <c r="L43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" s="3">
         <v>1</v>
@@ -5725,10 +5725,10 @@
         <v>1</v>
       </c>
       <c r="P43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" s="3">
         <v>1</v>
@@ -5737,10 +5737,10 @@
         <v>1</v>
       </c>
       <c r="T43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
         <v>1</v>
@@ -5749,10 +5749,10 @@
         <v>1</v>
       </c>
       <c r="X43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3">
         <v>1</v>
@@ -5761,13 +5761,13 @@
         <v>1</v>
       </c>
       <c r="AB43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
@@ -5782,13 +5782,13 @@
         <v>0</v>
       </c>
       <c r="AI43" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.2">
@@ -5799,10 +5799,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3">
         <v>1</v>
@@ -5811,10 +5811,10 @@
         <v>1</v>
       </c>
       <c r="G44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3">
         <v>1</v>
@@ -5823,10 +5823,10 @@
         <v>1</v>
       </c>
       <c r="K44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="3">
         <v>1</v>
@@ -5835,10 +5835,10 @@
         <v>1</v>
       </c>
       <c r="O44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
@@ -5847,10 +5847,10 @@
         <v>1</v>
       </c>
       <c r="S44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3">
         <v>1</v>
@@ -5859,10 +5859,10 @@
         <v>1</v>
       </c>
       <c r="W44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="3">
         <v>1</v>
@@ -5871,13 +5871,13 @@
         <v>1</v>
       </c>
       <c r="AA44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
@@ -5892,16 +5892,16 @@
         <v>0</v>
       </c>
       <c r="AH44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.2">
@@ -5909,10 +5909,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="3">
         <v>1</v>
@@ -5921,10 +5921,10 @@
         <v>1</v>
       </c>
       <c r="F45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
         <v>1</v>
@@ -5933,10 +5933,10 @@
         <v>1</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3">
         <v>1</v>
@@ -5945,10 +5945,10 @@
         <v>1</v>
       </c>
       <c r="N45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" s="3">
         <v>1</v>
@@ -5957,10 +5957,10 @@
         <v>1</v>
       </c>
       <c r="R45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
         <v>1</v>
@@ -5969,10 +5969,10 @@
         <v>1</v>
       </c>
       <c r="V45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
         <v>1</v>
@@ -5981,13 +5981,13 @@
         <v>1</v>
       </c>
       <c r="Z45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -6002,16 +6002,16 @@
         <v>0</v>
       </c>
       <c r="AG45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK45" s="2">
         <v>0</v>
@@ -6022,7 +6022,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -6031,10 +6031,10 @@
         <v>1</v>
       </c>
       <c r="E46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
@@ -6043,10 +6043,10 @@
         <v>1</v>
       </c>
       <c r="I46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="3">
         <v>1</v>
@@ -6055,10 +6055,10 @@
         <v>1</v>
       </c>
       <c r="M46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" s="3">
         <v>1</v>
@@ -6067,10 +6067,10 @@
         <v>1</v>
       </c>
       <c r="Q46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" s="3">
         <v>1</v>
@@ -6079,10 +6079,10 @@
         <v>1</v>
       </c>
       <c r="U46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" s="3">
         <v>1</v>
@@ -6091,13 +6091,13 @@
         <v>1</v>
       </c>
       <c r="Y46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB46" s="3">
         <v>0</v>
@@ -6112,16 +6112,16 @@
         <v>0</v>
       </c>
       <c r="AF46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ46" s="3">
         <v>0</v>
@@ -6141,10 +6141,10 @@
         <v>1</v>
       </c>
       <c r="D47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
@@ -6153,10 +6153,10 @@
         <v>1</v>
       </c>
       <c r="H47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
         <v>1</v>
@@ -6165,10 +6165,10 @@
         <v>1</v>
       </c>
       <c r="L47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -6177,10 +6177,10 @@
         <v>1</v>
       </c>
       <c r="P47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3">
         <v>1</v>
@@ -6189,10 +6189,10 @@
         <v>1</v>
       </c>
       <c r="T47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="3">
         <v>1</v>
@@ -6201,13 +6201,13 @@
         <v>1</v>
       </c>
       <c r="X47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -6222,16 +6222,16 @@
         <v>0</v>
       </c>
       <c r="AE47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI47" s="4">
         <v>0</v>
@@ -6251,10 +6251,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <v>1</v>
@@ -6263,10 +6263,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <v>1</v>
@@ -6275,10 +6275,10 @@
         <v>1</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3">
         <v>1</v>
@@ -6287,10 +6287,10 @@
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
@@ -6299,10 +6299,10 @@
         <v>1</v>
       </c>
       <c r="S48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" s="3">
         <v>1</v>
@@ -6311,13 +6311,13 @@
         <v>1</v>
       </c>
       <c r="W48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -6332,16 +6332,16 @@
         <v>0</v>
       </c>
       <c r="AD48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48" s="3">
         <v>0</v>
@@ -6361,10 +6361,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -6373,10 +6373,10 @@
         <v>1</v>
       </c>
       <c r="F49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>1</v>
@@ -6385,10 +6385,10 @@
         <v>1</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>1</v>
@@ -6397,10 +6397,10 @@
         <v>1</v>
       </c>
       <c r="N49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>1</v>
@@ -6409,10 +6409,10 @@
         <v>1</v>
       </c>
       <c r="R49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
@@ -6421,13 +6421,13 @@
         <v>1</v>
       </c>
       <c r="V49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -6442,16 +6442,16 @@
         <v>0</v>
       </c>
       <c r="AC49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG49" s="3">
         <v>0</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:37" x14ac:dyDescent="0.2">
@@ -6474,7 +6474,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -6483,10 +6483,10 @@
         <v>1</v>
       </c>
       <c r="E50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -6495,10 +6495,10 @@
         <v>1</v>
       </c>
       <c r="I50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" s="3">
         <v>1</v>
@@ -6507,10 +6507,10 @@
         <v>1</v>
       </c>
       <c r="M50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="3">
         <v>1</v>
@@ -6519,10 +6519,10 @@
         <v>1</v>
       </c>
       <c r="Q50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="3">
         <v>1</v>
@@ -6531,13 +6531,13 @@
         <v>1</v>
       </c>
       <c r="U50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="3">
         <v>0</v>
@@ -6552,16 +6552,16 @@
         <v>0</v>
       </c>
       <c r="AB50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" s="3">
         <v>0</v>
@@ -6576,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="AJ50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:37" x14ac:dyDescent="0.2">
@@ -6593,10 +6593,10 @@
         <v>1</v>
       </c>
       <c r="D51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="3">
         <v>1</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="H51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="3">
         <v>1</v>
@@ -6617,10 +6617,10 @@
         <v>1</v>
       </c>
       <c r="L51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="3">
         <v>1</v>
@@ -6629,10 +6629,10 @@
         <v>1</v>
       </c>
       <c r="P51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="3">
         <v>1</v>
@@ -6641,13 +6641,13 @@
         <v>1</v>
       </c>
       <c r="T51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="3">
         <v>0</v>
@@ -6662,16 +6662,16 @@
         <v>0</v>
       </c>
       <c r="AA51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE51" s="3">
         <v>0</v>
@@ -6686,13 +6686,13 @@
         <v>0</v>
       </c>
       <c r="AI51" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:37" x14ac:dyDescent="0.2">
@@ -6703,10 +6703,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>1</v>
@@ -6715,10 +6715,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>1</v>
@@ -6727,10 +6727,10 @@
         <v>1</v>
       </c>
       <c r="K52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
         <v>1</v>
@@ -6739,10 +6739,10 @@
         <v>1</v>
       </c>
       <c r="O52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>1</v>
@@ -6751,13 +6751,13 @@
         <v>1</v>
       </c>
       <c r="S52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -6772,16 +6772,16 @@
         <v>0</v>
       </c>
       <c r="Z52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -6796,16 +6796,16 @@
         <v>0</v>
       </c>
       <c r="AH52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI52" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:37" x14ac:dyDescent="0.2">
@@ -6813,10 +6813,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
@@ -6825,10 +6825,10 @@
         <v>1</v>
       </c>
       <c r="F53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
@@ -6837,10 +6837,10 @@
         <v>1</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3">
         <v>1</v>
@@ -6849,10 +6849,10 @@
         <v>1</v>
       </c>
       <c r="N53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" s="3">
         <v>1</v>
@@ -6861,13 +6861,13 @@
         <v>1</v>
       </c>
       <c r="R53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U53" s="3">
         <v>0</v>
@@ -6882,16 +6882,16 @@
         <v>0</v>
       </c>
       <c r="Y53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC53" s="3">
         <v>0</v>
@@ -6906,16 +6906,16 @@
         <v>0</v>
       </c>
       <c r="AG53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK53" s="2">
         <v>0</v>
@@ -6926,7 +6926,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -6935,10 +6935,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="3">
         <v>1</v>
@@ -6947,10 +6947,10 @@
         <v>1</v>
       </c>
       <c r="I54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="3">
         <v>1</v>
@@ -6959,10 +6959,10 @@
         <v>1</v>
       </c>
       <c r="M54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="3">
         <v>1</v>
@@ -6971,13 +6971,13 @@
         <v>1</v>
       </c>
       <c r="Q54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="3">
         <v>0</v>
@@ -6992,16 +6992,16 @@
         <v>0</v>
       </c>
       <c r="X54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB54" s="3">
         <v>0</v>
@@ -7016,16 +7016,16 @@
         <v>0</v>
       </c>
       <c r="AF54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ54" s="3">
         <v>0</v>
@@ -7045,10 +7045,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="3">
         <v>1</v>
@@ -7057,10 +7057,10 @@
         <v>1</v>
       </c>
       <c r="H55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3">
         <v>1</v>
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="L55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="3">
         <v>1</v>
@@ -7081,13 +7081,13 @@
         <v>1</v>
       </c>
       <c r="P55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" s="3">
         <v>0</v>
@@ -7102,16 +7102,16 @@
         <v>0</v>
       </c>
       <c r="W55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA55" s="3">
         <v>0</v>
@@ -7126,16 +7126,16 @@
         <v>0</v>
       </c>
       <c r="AE55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI55" s="4">
         <v>0</v>
@@ -7155,10 +7155,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="3">
         <v>1</v>
@@ -7167,10 +7167,10 @@
         <v>1</v>
       </c>
       <c r="G56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="3">
         <v>1</v>
@@ -7179,10 +7179,10 @@
         <v>1</v>
       </c>
       <c r="K56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="3">
         <v>1</v>
@@ -7191,13 +7191,13 @@
         <v>1</v>
       </c>
       <c r="O56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="3">
         <v>0</v>
@@ -7212,16 +7212,16 @@
         <v>0</v>
       </c>
       <c r="V56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z56" s="3">
         <v>0</v>
@@ -7236,16 +7236,16 @@
         <v>0</v>
       </c>
       <c r="AD56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH56" s="3">
         <v>0</v>
@@ -7265,10 +7265,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
@@ -7277,10 +7277,10 @@
         <v>1</v>
       </c>
       <c r="F57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
         <v>1</v>
@@ -7289,10 +7289,10 @@
         <v>1</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>1</v>
@@ -7301,13 +7301,13 @@
         <v>1</v>
       </c>
       <c r="N57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -7322,16 +7322,16 @@
         <v>0</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
@@ -7346,16 +7346,16 @@
         <v>0</v>
       </c>
       <c r="AC57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG57" s="3">
         <v>0</v>
@@ -7370,7 +7370,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:37" x14ac:dyDescent="0.2">
@@ -7378,7 +7378,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -7387,10 +7387,10 @@
         <v>1</v>
       </c>
       <c r="E58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>1</v>
@@ -7399,10 +7399,10 @@
         <v>1</v>
       </c>
       <c r="I58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>1</v>
@@ -7411,13 +7411,13 @@
         <v>1</v>
       </c>
       <c r="M58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -7432,16 +7432,16 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -7456,16 +7456,16 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -7480,10 +7480,10 @@
         <v>0</v>
       </c>
       <c r="AJ58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:37" x14ac:dyDescent="0.2">
@@ -7497,10 +7497,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
         <v>1</v>
@@ -7509,10 +7509,10 @@
         <v>1</v>
       </c>
       <c r="H59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3">
         <v>1</v>
@@ -7521,13 +7521,13 @@
         <v>1</v>
       </c>
       <c r="L59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
@@ -7542,16 +7542,16 @@
         <v>0</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -7566,16 +7566,16 @@
         <v>0</v>
       </c>
       <c r="AA59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -7590,13 +7590,13 @@
         <v>0</v>
       </c>
       <c r="AI59" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:37" x14ac:dyDescent="0.2">
@@ -7607,10 +7607,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="3">
         <v>1</v>
@@ -7619,10 +7619,10 @@
         <v>1</v>
       </c>
       <c r="G60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" s="3">
         <v>1</v>
@@ -7631,13 +7631,13 @@
         <v>1</v>
       </c>
       <c r="K60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" s="3">
         <v>0</v>
@@ -7652,16 +7652,16 @@
         <v>0</v>
       </c>
       <c r="R60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="3">
         <v>0</v>
@@ -7676,16 +7676,16 @@
         <v>0</v>
       </c>
       <c r="Z60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD60" s="3">
         <v>0</v>
@@ -7700,16 +7700,16 @@
         <v>0</v>
       </c>
       <c r="AH60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI60" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:37" x14ac:dyDescent="0.2">
@@ -7717,10 +7717,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" s="3">
         <v>1</v>
@@ -7729,10 +7729,10 @@
         <v>1</v>
       </c>
       <c r="F61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>1</v>
@@ -7741,13 +7741,13 @@
         <v>1</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -7762,16 +7762,16 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -7786,16 +7786,16 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -7810,16 +7810,16 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI61" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK61" s="2">
         <v>0</v>
